--- a/data/trans_orig/P1414-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2012</t>
+          <t>Población con diagnóstico de fibromialgia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>599102</t>
+          <t>598919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609260</t>
+          <t>609218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1285229</t>
+          <t>1285878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1295723</t>
+          <t>1296305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>679855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>681863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684860</t>
+          <t>685560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701339</t>
+          <t>701524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1367135</t>
+          <t>1366714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1383314</t>
+          <t>1383159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37397</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38999</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607734</t>
+          <t>607596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>576867</t>
+          <t>576621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598156</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1189881</t>
+          <t>1190326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211092</t>
+          <t>1211689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44085</t>
+          <t>44827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422419</t>
+          <t>421957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>406685</t>
+          <t>406701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428500</t>
+          <t>428060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>833144</t>
+          <t>832402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>856629</t>
+          <t>855654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>21029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302092</t>
+          <t>302235</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333730</t>
+          <t>334124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347950</t>
+          <t>347157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>641053</t>
+          <t>641787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>655761</t>
+          <t>655933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243541</t>
+          <t>244529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372120</t>
+          <t>372304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384585</t>
+          <t>384579</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>619979</t>
+          <t>620347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>634187</t>
+          <t>634327</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>74465</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>113465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>122298</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3412614</t>
+          <t>3412028</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3423680</t>
+          <t>3423623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3441052</t>
+          <t>3440667</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3479586</t>
+          <t>3479667</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6855081</t>
+          <t>6858613</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6897829</t>
+          <t>6899278</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2016</t>
+          <t>Población con diagnóstico de fibromialgia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4555</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>953</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5423</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5370</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390332</t>
+          <t>391200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809848</t>
+          <t>811387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582484</t>
+          <t>581648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555532</t>
+          <t>555698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562624</t>
+          <t>562634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1142241</t>
+          <t>1141992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152028</t>
+          <t>1152001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645653</t>
+          <t>646197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657790</t>
+          <t>657899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315964</t>
+          <t>1314551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326988</t>
+          <t>1326987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26553</t>
+          <t>26076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51875</t>
+          <t>50754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56005</t>
+          <t>55447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635701</t>
+          <t>635942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644968</t>
+          <t>644966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597202</t>
+          <t>598323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622524</t>
+          <t>623001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1239120</t>
+          <t>1239678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1265684</t>
+          <t>1265307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58072</t>
+          <t>58508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63054</t>
+          <t>63129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466734</t>
+          <t>467232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476861</t>
+          <t>476727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>438777</t>
+          <t>438341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>466100</t>
+          <t>464832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>911713</t>
+          <t>911638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>940306</t>
+          <t>939665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324314</t>
+          <t>325337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>345997</t>
+          <t>346965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>364344</t>
+          <t>364710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>677665</t>
+          <t>677298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>696993</t>
+          <t>697445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379873</t>
+          <t>379744</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394997</t>
+          <t>395036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634955</t>
+          <t>635145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651656</t>
+          <t>651013</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150014</t>
+          <t>148355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117905</t>
+          <t>117704</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165636</t>
+          <t>165178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3370360</t>
+          <t>3369382</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3386166</t>
+          <t>3386614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3394528</t>
+          <t>3396187</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3440315</t>
+          <t>3441097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6773256</t>
+          <t>6773714</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6820987</t>
+          <t>6821188</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2023</t>
+          <t>Población con diagnóstico de fibromialgia en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,82 +6690,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7974</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305226</t>
+          <t>304308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703357</t>
+          <t>703323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417138</t>
+          <t>418196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506168</t>
+          <t>505688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927157</t>
+          <t>927403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934298</t>
+          <t>934310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>533136</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524074</t>
+          <t>523749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>534912</t>
+          <t>534709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1059149</t>
+          <t>1058795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069567</t>
+          <t>1069457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35091</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>43940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871860</t>
+          <t>872569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885704</t>
+          <t>885697</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674216</t>
+          <t>673104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689936</t>
+          <t>689830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1552122</t>
+          <t>1552097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1578208</t>
+          <t>1577728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37079</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55705</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61520</t>
+          <t>60518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549369</t>
+          <t>550169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558072</t>
+          <t>558094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485692</t>
+          <t>484661</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>504318</t>
+          <t>503750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1039592</t>
+          <t>1040594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1061078</t>
+          <t>1060823</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>58388</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53328</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359251</t>
+          <t>359209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365094</t>
+          <t>365095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>547811</t>
+          <t>547052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593038</t>
+          <t>593753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>918261</t>
+          <t>918262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953734</t>
+          <t>951503</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>279170</t>
+          <t>279208</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400200</t>
+          <t>399988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>412306</t>
+          <t>411751</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681851</t>
+          <t>681390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>693301</t>
+          <t>693380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111809</t>
+          <t>112384</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161825</t>
+          <t>161418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128277</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175852</t>
+          <t>176545</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3428935</t>
+          <t>3428220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3444509</t>
+          <t>3444667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3484150</t>
+          <t>3484557</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3534166</t>
+          <t>3533591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6923064</t>
+          <t>6922371</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6970639</t>
+          <t>6969759</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1414-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Edad-trans_orig.xlsx
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598919</t>
+          <t>598675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609218</t>
+          <t>609214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1285878</t>
+          <t>1285900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296305</t>
+          <t>1296296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24014</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>685560</t>
+          <t>685414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701524</t>
+          <t>700741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1366714</t>
+          <t>1367333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1383159</t>
+          <t>1382721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37643</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607596</t>
+          <t>607466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>576621</t>
+          <t>578308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598199</t>
+          <t>598526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1190326</t>
+          <t>1190496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211689</t>
+          <t>1210917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>40609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44827</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421957</t>
+          <t>421954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>406701</t>
+          <t>407191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428060</t>
+          <t>429002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>832402</t>
+          <t>833864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>855654</t>
+          <t>856856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302235</t>
+          <t>302181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334124</t>
+          <t>333770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347157</t>
+          <t>347045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>641787</t>
+          <t>641555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>655933</t>
+          <t>655703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244529</t>
+          <t>245572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372304</t>
+          <t>371981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384579</t>
+          <t>384588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>620347</t>
+          <t>621196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>634327</t>
+          <t>634380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74465</t>
+          <t>74492</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>113465</t>
+          <t>112317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122298</t>
+          <t>122212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3412028</t>
+          <t>3411936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3423623</t>
+          <t>3423678</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3440667</t>
+          <t>3441815</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3479667</t>
+          <t>3479640</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6858613</t>
+          <t>6858699</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6899278</t>
+          <t>6899928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391200</t>
+          <t>390584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>811387</t>
+          <t>810404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581648</t>
+          <t>581809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589536</t>
+          <t>589531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555698</t>
+          <t>554798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562634</t>
+          <t>562628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1141992</t>
+          <t>1142006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152001</t>
+          <t>1152038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646197</t>
+          <t>646165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657899</t>
+          <t>657737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314551</t>
+          <t>1314686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326987</t>
+          <t>1326969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26076</t>
+          <t>25627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50754</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55447</t>
+          <t>57368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635942</t>
+          <t>635540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644966</t>
+          <t>644956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598323</t>
+          <t>598053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623001</t>
+          <t>623450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1239678</t>
+          <t>1237757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1265307</t>
+          <t>1265249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58508</t>
+          <t>57828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63129</t>
+          <t>63009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467232</t>
+          <t>467260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476727</t>
+          <t>476723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>438341</t>
+          <t>439021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>464832</t>
+          <t>465097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>911638</t>
+          <t>911758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>939665</t>
+          <t>938262</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>34314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325337</t>
+          <t>323949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>346965</t>
+          <t>346233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>364710</t>
+          <t>364240</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>677298</t>
+          <t>677778</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>697445</t>
+          <t>697376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379744</t>
+          <t>379755</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395036</t>
+          <t>394983</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635145</t>
+          <t>636592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651013</t>
+          <t>652017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>104683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>152413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117704</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165178</t>
+          <t>163638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3369382</t>
+          <t>3371007</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3386614</t>
+          <t>3386386</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3396187</t>
+          <t>3392129</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3441097</t>
+          <t>3439859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6773714</t>
+          <t>6775254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6821188</t>
+          <t>6820673</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,27 +6833,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>311579</t>
+          <t>360480</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304308</t>
+          <t>352337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>711566</t>
+          <t>768273</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703323</t>
+          <t>758443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -7141,27 +7141,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422279</t>
+          <t>475525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418196</t>
+          <t>469454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7176,27 +7176,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>509963</t>
+          <t>498625</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>505688</t>
+          <t>494183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510922</t>
+          <t>500420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>932241</t>
+          <t>974150</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927403</t>
+          <t>968634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934310</t>
+          <t>976432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510922</t>
+          <t>500420</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510922</t>
+          <t>500420</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510922</t>
+          <t>500420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934469</t>
+          <t>977310</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934469</t>
+          <t>977310</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934469</t>
+          <t>977310</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>530227</t>
+          <t>608224</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523749</t>
+          <t>601697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>534709</t>
+          <t>613364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1065244</t>
+          <t>1227663</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1058795</t>
+          <t>1221620</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069457</t>
+          <t>1232925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540944</t>
+          <t>619984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540944</t>
+          <t>619984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540944</t>
+          <t>619984</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1075961</t>
+          <t>1239423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1075961</t>
+          <t>1239423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1075961</t>
+          <t>1239423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>29143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36203</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32113</t>
+          <t>34581</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>881489</t>
+          <t>694083</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872569</t>
+          <t>685683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885697</t>
+          <t>698347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>682434</t>
+          <t>702450</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673104</t>
+          <t>693086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689830</t>
+          <t>709931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1563924</t>
+          <t>1396533</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1552097</t>
+          <t>1385177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1577728</t>
+          <t>1405490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709307</t>
+          <t>731593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709307</t>
+          <t>731593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709307</t>
+          <t>731593</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1596037</t>
+          <t>1431114</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1596037</t>
+          <t>1431114</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1596037</t>
+          <t>1431114</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56736</t>
+          <t>62574</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,17 +8127,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>54993</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40289</t>
+          <t>44801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>66797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>555401</t>
+          <t>603410</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>550169</t>
+          <t>597743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>558094</t>
+          <t>606168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>495763</t>
+          <t>552112</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>484661</t>
+          <t>540163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>503750</t>
+          <t>562801</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,17 +8240,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1051163</t>
+          <t>1155522</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1040594</t>
+          <t>1143718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1060823</t>
+          <t>1165714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559716</t>
+          <t>607778</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559716</t>
+          <t>607778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559716</t>
+          <t>607778</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541397</t>
+          <t>602737</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541397</t>
+          <t>602737</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541397</t>
+          <t>602737</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1101112</t>
+          <t>1210515</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1101112</t>
+          <t>1210515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1101112</t>
+          <t>1210515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35702</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>31273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58388</t>
+          <t>48260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20086</t>
+          <t>33697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>52901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>363182</t>
+          <t>401739</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>359209</t>
+          <t>398035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365095</t>
+          <t>403763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>569738</t>
+          <t>396753</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>547052</t>
+          <t>387750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593753</t>
+          <t>404737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>932919</t>
+          <t>798493</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>918262</t>
+          <t>787923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>951503</t>
+          <t>807127</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366149</t>
+          <t>404814</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366149</t>
+          <t>404814</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366149</t>
+          <t>404814</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>605440</t>
+          <t>436010</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>605440</t>
+          <t>436010</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>605440</t>
+          <t>436010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>971589</t>
+          <t>840824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>971589</t>
+          <t>840824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>971589</t>
+          <t>840824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>521</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -8856,27 +8856,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>281281</t>
+          <t>308487</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>279208</t>
+          <t>305902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>281794</t>
+          <t>309008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>406662</t>
+          <t>442674</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>399988</t>
+          <t>434816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411751</t>
+          <t>448726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>687942</t>
+          <t>751161</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681390</t>
+          <t>743224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>693380</t>
+          <t>756678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281794</t>
+          <t>309008</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281794</t>
+          <t>309008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281794</t>
+          <t>309008</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424766</t>
+          <t>463004</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424766</t>
+          <t>463004</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424766</t>
+          <t>463004</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706560</t>
+          <t>772012</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706560</t>
+          <t>772012</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706560</t>
+          <t>772012</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>139611</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>137214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161418</t>
+          <t>175174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>153915</t>
+          <t>169709</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>149484</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176545</t>
+          <t>190076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3438636</t>
+          <t>3510476</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3428220</t>
+          <t>3500317</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3444667</t>
+          <t>3516492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3506364</t>
+          <t>3561318</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3484557</t>
+          <t>3541086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3533591</t>
+          <t>3579046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6945001</t>
+          <t>7071794</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6922371</t>
+          <t>7051427</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6969759</t>
+          <t>7092019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
